--- a/data/nzd0093/nzd0093.xlsx
+++ b/data/nzd0093/nzd0093.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J316"/>
+  <dimension ref="A1:J317"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11754,7 +11754,7 @@
         </is>
       </c>
       <c r="B315" t="n">
-        <v>399.62</v>
+        <v>397.08</v>
       </c>
       <c r="C315" t="n">
         <v>368.97</v>
@@ -11790,7 +11790,7 @@
         </is>
       </c>
       <c r="B316" t="n">
-        <v>404.98</v>
+        <v>395.51</v>
       </c>
       <c r="C316" t="n">
         <v>370.27</v>
@@ -11814,6 +11814,42 @@
         <v>365.31</v>
       </c>
       <c r="J316" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="317">
+      <c r="A317" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-07 22:12:09+00:00</t>
+        </is>
+      </c>
+      <c r="B317" t="n">
+        <v>398.43</v>
+      </c>
+      <c r="C317" t="n">
+        <v>374.3</v>
+      </c>
+      <c r="D317" t="n">
+        <v>368.24</v>
+      </c>
+      <c r="E317" t="n">
+        <v>360.01</v>
+      </c>
+      <c r="F317" t="n">
+        <v>354.15</v>
+      </c>
+      <c r="G317" t="n">
+        <v>357.22</v>
+      </c>
+      <c r="H317" t="n">
+        <v>365.47</v>
+      </c>
+      <c r="I317" t="n">
+        <v>368</v>
+      </c>
+      <c r="J317" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -11830,7 +11866,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B329"/>
+  <dimension ref="A1:B330"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15123,6 +15159,16 @@
       </c>
       <c r="B329" t="n">
         <v>0.12</v>
+      </c>
+    </row>
+    <row r="330">
+      <c r="A330" t="inlineStr">
+        <is>
+          <t>2025-12-07 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B330" t="n">
+        <v>1.14</v>
       </c>
     </row>
   </sheetData>
@@ -15291,28 +15337,28 @@
         <v>0.0154</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.2683777551699648</v>
+        <v>-0.2885140839588363</v>
       </c>
       <c r="J2" t="n">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="K2" t="n">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="L2" t="n">
-        <v>0.0228288070382866</v>
+        <v>0.02607506094589063</v>
       </c>
       <c r="M2" t="n">
-        <v>9.745790634017451</v>
+        <v>9.827199072578836</v>
       </c>
       <c r="N2" t="n">
-        <v>161.4867083053956</v>
+        <v>163.474914298112</v>
       </c>
       <c r="O2" t="n">
-        <v>12.7077420616487</v>
+        <v>12.78573088634795</v>
       </c>
       <c r="P2" t="n">
-        <v>424.7084781988536</v>
+        <v>424.9207057371773</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -15369,28 +15415,28 @@
         <v>0.0622</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.1953623608325873</v>
+        <v>-0.1928074739538155</v>
       </c>
       <c r="J3" t="n">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="K3" t="n">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="L3" t="n">
-        <v>0.06521809065542872</v>
+        <v>0.06394674695397817</v>
       </c>
       <c r="M3" t="n">
-        <v>3.922906712117429</v>
+        <v>3.918872885106965</v>
       </c>
       <c r="N3" t="n">
-        <v>28.65367432633723</v>
+        <v>28.61190387318213</v>
       </c>
       <c r="O3" t="n">
-        <v>5.352912695564652</v>
+        <v>5.349009616104848</v>
       </c>
       <c r="P3" t="n">
-        <v>375.4635963418821</v>
+        <v>375.4366213854898</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -15447,28 +15493,28 @@
         <v>0.07290000000000001</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.1094946233344865</v>
+        <v>-0.1095033021717985</v>
       </c>
       <c r="J4" t="n">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="K4" t="n">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="L4" t="n">
-        <v>0.04239580137466425</v>
+        <v>0.04268710352703042</v>
       </c>
       <c r="M4" t="n">
-        <v>2.882854436491648</v>
+        <v>2.873782875173069</v>
       </c>
       <c r="N4" t="n">
-        <v>14.18420804531038</v>
+        <v>14.13932187532805</v>
       </c>
       <c r="O4" t="n">
-        <v>3.766192778564366</v>
+        <v>3.76022896581153</v>
       </c>
       <c r="P4" t="n">
-        <v>371.1242165618957</v>
+        <v>371.1243081946251</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -15525,28 +15571,28 @@
         <v>0.0675</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.07107358407215428</v>
+        <v>-0.07165576506620268</v>
       </c>
       <c r="J5" t="n">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="K5" t="n">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="L5" t="n">
-        <v>0.01245031259964058</v>
+        <v>0.01273865876775804</v>
       </c>
       <c r="M5" t="n">
-        <v>3.50393620712673</v>
+        <v>3.496094649379423</v>
       </c>
       <c r="N5" t="n">
-        <v>20.98705230837231</v>
+        <v>20.92317699370133</v>
       </c>
       <c r="O5" t="n">
-        <v>4.581162768159664</v>
+        <v>4.574185937814654</v>
       </c>
       <c r="P5" t="n">
-        <v>362.7746871437734</v>
+        <v>362.7808339156941</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -15603,28 +15649,28 @@
         <v>0.0752</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.06696984262153137</v>
+        <v>-0.06768378270200395</v>
       </c>
       <c r="J6" t="n">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="K6" t="n">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="L6" t="n">
-        <v>0.008479643623329758</v>
+        <v>0.008718867375264061</v>
       </c>
       <c r="M6" t="n">
-        <v>4.132436791610403</v>
+        <v>4.122587605842617</v>
       </c>
       <c r="N6" t="n">
-        <v>27.46875040501338</v>
+        <v>27.38564289417376</v>
       </c>
       <c r="O6" t="n">
-        <v>5.241063861947628</v>
+        <v>5.233129359587221</v>
       </c>
       <c r="P6" t="n">
-        <v>357.0109560214969</v>
+        <v>357.0184939296124</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -15681,28 +15727,28 @@
         <v>0.1169</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.07645911109310802</v>
+        <v>-0.07489485780886124</v>
       </c>
       <c r="J7" t="n">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="K7" t="n">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="L7" t="n">
-        <v>0.0221793127873352</v>
+        <v>0.02141793152061144</v>
       </c>
       <c r="M7" t="n">
-        <v>2.701718296994034</v>
+        <v>2.699763408551644</v>
       </c>
       <c r="N7" t="n">
-        <v>13.49975655276151</v>
+        <v>13.47536867834873</v>
       </c>
       <c r="O7" t="n">
-        <v>3.674201485052433</v>
+        <v>3.670881185539615</v>
       </c>
       <c r="P7" t="n">
-        <v>356.8024883191472</v>
+        <v>356.7859726508882</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -15759,28 +15805,28 @@
         <v>0.07389999999999999</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.005696234349197494</v>
+        <v>-0.004560970797629595</v>
       </c>
       <c r="J8" t="n">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="K8" t="n">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="L8" t="n">
-        <v>0.0001090839037665159</v>
+        <v>7.038891907940048e-05</v>
       </c>
       <c r="M8" t="n">
-        <v>2.890365036868237</v>
+        <v>2.886012919145446</v>
       </c>
       <c r="N8" t="n">
-        <v>15.33199581566311</v>
+        <v>15.29261202107509</v>
       </c>
       <c r="O8" t="n">
-        <v>3.915609252167932</v>
+        <v>3.910576942226695</v>
       </c>
       <c r="P8" t="n">
-        <v>363.889580705158</v>
+        <v>363.8774531882223</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -15837,28 +15883,28 @@
         <v>0.09520000000000001</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.1522117629891631</v>
+        <v>-0.1503161384738174</v>
       </c>
       <c r="J9" t="n">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="K9" t="n">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="L9" t="n">
-        <v>0.06033976703211208</v>
+        <v>0.05924362899113456</v>
       </c>
       <c r="M9" t="n">
-        <v>3.235665095425991</v>
+        <v>3.233294203663093</v>
       </c>
       <c r="N9" t="n">
-        <v>18.8981792036399</v>
+        <v>18.86529768959175</v>
       </c>
       <c r="O9" t="n">
-        <v>4.347203607336548</v>
+        <v>4.343420045262921</v>
       </c>
       <c r="P9" t="n">
-        <v>369.0594105057946</v>
+        <v>369.039396160321</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -15896,7 +15942,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J316"/>
+  <dimension ref="A1:J317"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -32227,7 +32273,7 @@
       </c>
       <c r="B315" t="inlineStr">
         <is>
-          <t>-35.636412299282675,174.53058429841766</t>
+          <t>-35.63640426478364,174.530610562315</t>
         </is>
       </c>
       <c r="C315" t="inlineStr">
@@ -32279,7 +32325,7 @@
       </c>
       <c r="B316" t="inlineStr">
         <is>
-          <t>-35.63642925395515,174.5305288753723</t>
+          <t>-35.63639929857475,174.53062679629605</t>
         </is>
       </c>
       <c r="C316" t="inlineStr">
@@ -32318,6 +32364,58 @@
         </is>
       </c>
       <c r="J316" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="317">
+      <c r="A317" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-07 22:12:09+00:00</t>
+        </is>
+      </c>
+      <c r="B317" t="inlineStr">
+        <is>
+          <t>-35.63640853508894,174.53059660315765</t>
+        </is>
+      </c>
+      <c r="C317" t="inlineStr">
+        <is>
+          <t>-35.63567240210473,174.53055393160105</t>
+        </is>
+      </c>
+      <c r="D317" t="inlineStr">
+        <is>
+          <t>-35.63513237704528,174.5300194964496</t>
+        </is>
+      </c>
+      <c r="E317" t="inlineStr">
+        <is>
+          <t>-35.63475705461019,174.52926236799914</t>
+        </is>
+      </c>
+      <c r="F317" t="inlineStr">
+        <is>
+          <t>-35.63456322692522,174.52838426454883</t>
+        </is>
+      </c>
+      <c r="G317" t="inlineStr">
+        <is>
+          <t>-35.63463138323599,174.527479511164</t>
+        </is>
+      </c>
+      <c r="H317" t="inlineStr">
+        <is>
+          <t>-35.63476475363227,174.52659243304686</t>
+        </is>
+      </c>
+      <c r="I317" t="inlineStr">
+        <is>
+          <t>-35.63487025465826,174.52570418898662</t>
+        </is>
+      </c>
+      <c r="J317" t="inlineStr">
         <is>
           <t>L9</t>
         </is>

--- a/data/nzd0093/nzd0093.xlsx
+++ b/data/nzd0093/nzd0093.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J317"/>
+  <dimension ref="A1:J320"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11850,6 +11850,114 @@
         <v>368</v>
       </c>
       <c r="J317" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="318">
+      <c r="A318" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-08 22:12:06+00:00</t>
+        </is>
+      </c>
+      <c r="B318" t="n">
+        <v>398.93</v>
+      </c>
+      <c r="C318" t="n">
+        <v>375.34</v>
+      </c>
+      <c r="D318" t="n">
+        <v>368.49</v>
+      </c>
+      <c r="E318" t="n">
+        <v>361.77</v>
+      </c>
+      <c r="F318" t="n">
+        <v>357.52</v>
+      </c>
+      <c r="G318" t="n">
+        <v>358.08</v>
+      </c>
+      <c r="H318" t="n">
+        <v>365.74</v>
+      </c>
+      <c r="I318" t="n">
+        <v>368.41</v>
+      </c>
+      <c r="J318" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="319">
+      <c r="A319" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-16 22:11:57+00:00</t>
+        </is>
+      </c>
+      <c r="B319" t="n">
+        <v>412.05</v>
+      </c>
+      <c r="C319" t="n">
+        <v>375.44</v>
+      </c>
+      <c r="D319" t="n">
+        <v>368.93</v>
+      </c>
+      <c r="E319" t="n">
+        <v>362.75</v>
+      </c>
+      <c r="F319" t="n">
+        <v>358.8</v>
+      </c>
+      <c r="G319" t="n">
+        <v>357.95</v>
+      </c>
+      <c r="H319" t="n">
+        <v>366.41</v>
+      </c>
+      <c r="I319" t="n">
+        <v>368.17</v>
+      </c>
+      <c r="J319" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="320">
+      <c r="A320" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-24 22:12:07+00:00</t>
+        </is>
+      </c>
+      <c r="B320" t="n">
+        <v>412.05</v>
+      </c>
+      <c r="C320" t="n">
+        <v>373.11</v>
+      </c>
+      <c r="D320" t="n">
+        <v>368.97</v>
+      </c>
+      <c r="E320" t="n">
+        <v>362.9</v>
+      </c>
+      <c r="F320" t="n">
+        <v>359.07</v>
+      </c>
+      <c r="G320" t="n">
+        <v>357.96</v>
+      </c>
+      <c r="H320" t="n">
+        <v>366.12</v>
+      </c>
+      <c r="I320" t="n">
+        <v>368.75</v>
+      </c>
+      <c r="J320" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -11866,7 +11974,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B330"/>
+  <dimension ref="A1:B333"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15169,6 +15277,36 @@
       </c>
       <c r="B330" t="n">
         <v>1.14</v>
+      </c>
+    </row>
+    <row r="331">
+      <c r="A331" t="inlineStr">
+        <is>
+          <t>2026-01-08 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B331" t="n">
+        <v>0.73</v>
+      </c>
+    </row>
+    <row r="332">
+      <c r="A332" t="inlineStr">
+        <is>
+          <t>2026-01-16 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B332" t="n">
+        <v>-0.13</v>
+      </c>
+    </row>
+    <row r="333">
+      <c r="A333" t="inlineStr">
+        <is>
+          <t>2026-01-24 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B333" t="n">
+        <v>0.67</v>
       </c>
     </row>
   </sheetData>
@@ -15337,28 +15475,28 @@
         <v>0.0154</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.2885140839588363</v>
+        <v>-0.3068484816294428</v>
       </c>
       <c r="J2" t="n">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="K2" t="n">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="L2" t="n">
-        <v>0.02607506094589063</v>
+        <v>0.02977854863765528</v>
       </c>
       <c r="M2" t="n">
-        <v>9.827199072578836</v>
+        <v>9.836638070341939</v>
       </c>
       <c r="N2" t="n">
-        <v>163.474914298112</v>
+        <v>163.148513287883</v>
       </c>
       <c r="O2" t="n">
-        <v>12.78573088634795</v>
+        <v>12.77296023981454</v>
       </c>
       <c r="P2" t="n">
-        <v>424.9207057371773</v>
+        <v>425.1151051098108</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -15415,28 +15553,28 @@
         <v>0.0622</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.1928074739538155</v>
+        <v>-0.1847000430121691</v>
       </c>
       <c r="J3" t="n">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="K3" t="n">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="L3" t="n">
-        <v>0.06394674695397817</v>
+        <v>0.05980988400278353</v>
       </c>
       <c r="M3" t="n">
-        <v>3.918872885106965</v>
+        <v>3.908179251005012</v>
       </c>
       <c r="N3" t="n">
-        <v>28.61190387318213</v>
+        <v>28.51967237211483</v>
       </c>
       <c r="O3" t="n">
-        <v>5.349009616104848</v>
+        <v>5.340381294637568</v>
       </c>
       <c r="P3" t="n">
-        <v>375.4366213854898</v>
+        <v>375.3506354507362</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -15493,28 +15631,28 @@
         <v>0.07290000000000001</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.1095033021717985</v>
+        <v>-0.108457599042809</v>
       </c>
       <c r="J4" t="n">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="K4" t="n">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="L4" t="n">
-        <v>0.04268710352703042</v>
+        <v>0.04274553438250073</v>
       </c>
       <c r="M4" t="n">
-        <v>2.873782875173069</v>
+        <v>2.850792114474525</v>
       </c>
       <c r="N4" t="n">
-        <v>14.13932187532805</v>
+        <v>14.00955821789609</v>
       </c>
       <c r="O4" t="n">
-        <v>3.76022896581153</v>
+        <v>3.742934439433329</v>
       </c>
       <c r="P4" t="n">
-        <v>371.1243081946251</v>
+        <v>371.1132127406606</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -15571,28 +15709,28 @@
         <v>0.0675</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.07165576506620268</v>
+        <v>-0.06865499229346975</v>
       </c>
       <c r="J5" t="n">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="K5" t="n">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="L5" t="n">
-        <v>0.01273865876775804</v>
+        <v>0.01193572027860035</v>
       </c>
       <c r="M5" t="n">
-        <v>3.496094649379423</v>
+        <v>3.475614021095428</v>
       </c>
       <c r="N5" t="n">
-        <v>20.92317699370133</v>
+        <v>20.75145868873314</v>
       </c>
       <c r="O5" t="n">
-        <v>4.574185937814654</v>
+        <v>4.5553768986477</v>
       </c>
       <c r="P5" t="n">
-        <v>362.7808339156941</v>
+        <v>362.748995847115</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -15649,28 +15787,28 @@
         <v>0.0752</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.06768378270200395</v>
+        <v>-0.06154515935294589</v>
       </c>
       <c r="J6" t="n">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="K6" t="n">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="L6" t="n">
-        <v>0.008718867375264061</v>
+        <v>0.007344244088099305</v>
       </c>
       <c r="M6" t="n">
-        <v>4.122587605842617</v>
+        <v>4.115649824382222</v>
       </c>
       <c r="N6" t="n">
-        <v>27.38564289417376</v>
+        <v>27.22746332405548</v>
       </c>
       <c r="O6" t="n">
-        <v>5.233129359587221</v>
+        <v>5.217994185897056</v>
       </c>
       <c r="P6" t="n">
-        <v>357.0184939296124</v>
+        <v>356.953368163197</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -15727,28 +15865,28 @@
         <v>0.1169</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.07489485780886124</v>
+        <v>-0.06884687330814453</v>
       </c>
       <c r="J7" t="n">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="K7" t="n">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="L7" t="n">
-        <v>0.02141793152061144</v>
+        <v>0.01840918827317473</v>
       </c>
       <c r="M7" t="n">
-        <v>2.699763408551644</v>
+        <v>2.700232582439363</v>
       </c>
       <c r="N7" t="n">
-        <v>13.47536867834873</v>
+        <v>13.4410162449997</v>
       </c>
       <c r="O7" t="n">
-        <v>3.670881185539615</v>
+        <v>3.666199155119604</v>
       </c>
       <c r="P7" t="n">
-        <v>356.7859726508882</v>
+        <v>356.7218190361372</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -15805,28 +15943,28 @@
         <v>0.07389999999999999</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.004560970797629595</v>
+        <v>-5.696324037988919e-05</v>
       </c>
       <c r="J8" t="n">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="K8" t="n">
-        <v>314</v>
+        <v>317</v>
       </c>
       <c r="L8" t="n">
-        <v>7.038891907940048e-05</v>
+        <v>1.117551107210346e-08</v>
       </c>
       <c r="M8" t="n">
-        <v>2.886012919145446</v>
+        <v>2.878033382490156</v>
       </c>
       <c r="N8" t="n">
-        <v>15.29261202107509</v>
+        <v>15.19867233633172</v>
       </c>
       <c r="O8" t="n">
-        <v>3.910576942226695</v>
+        <v>3.898547464932513</v>
       </c>
       <c r="P8" t="n">
-        <v>363.8774531882223</v>
+        <v>363.829113958398</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -15883,28 +16021,28 @@
         <v>0.09520000000000001</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.1503161384738174</v>
+        <v>-0.1439314345783659</v>
       </c>
       <c r="J9" t="n">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="K9" t="n">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="L9" t="n">
-        <v>0.05924362899113456</v>
+        <v>0.05538316877496163</v>
       </c>
       <c r="M9" t="n">
-        <v>3.233294203663093</v>
+        <v>3.2288674116542</v>
       </c>
       <c r="N9" t="n">
-        <v>18.86529768959175</v>
+        <v>18.7913077473735</v>
       </c>
       <c r="O9" t="n">
-        <v>4.343420045262921</v>
+        <v>4.334894202558293</v>
       </c>
       <c r="P9" t="n">
-        <v>369.039396160321</v>
+        <v>368.97166783105</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -15942,7 +16080,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J317"/>
+  <dimension ref="A1:J320"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -32421,6 +32559,162 @@
         </is>
       </c>
     </row>
+    <row r="318">
+      <c r="A318" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-08 22:12:06+00:00</t>
+        </is>
+      </c>
+      <c r="B318" t="inlineStr">
+        <is>
+          <t>-35.63641011668311,174.53059143309895</t>
+        </is>
+      </c>
+      <c r="C318" t="inlineStr">
+        <is>
+          <t>-35.63567738870562,174.53054420703177</t>
+        </is>
+      </c>
+      <c r="D318" t="inlineStr">
+        <is>
+          <t>-35.63513420900486,174.53001788873664</t>
+        </is>
+      </c>
+      <c r="E318" t="inlineStr">
+        <is>
+          <t>-35.63477216415631,174.52925644142636</t>
+        </is>
+      </c>
+      <c r="F318" t="inlineStr">
+        <is>
+          <t>-35.63459355386071,174.5283820992</t>
+        </is>
+      </c>
+      <c r="G318" t="inlineStr">
+        <is>
+          <t>-35.63463911127154,174.5274802627755</t>
+        </is>
+      </c>
+      <c r="H318" t="inlineStr">
+        <is>
+          <t>-35.63476717332937,174.52659275443312</t>
+        </is>
+      </c>
+      <c r="I318" t="inlineStr">
+        <is>
+          <t>-35.63487392206298,174.52570475001187</t>
+        </is>
+      </c>
+      <c r="J318" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="319">
+      <c r="A319" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-16 22:11:57+00:00</t>
+        </is>
+      </c>
+      <c r="B319" t="inlineStr">
+        <is>
+          <t>-35.63645161763604,174.53045577068406</t>
+        </is>
+      </c>
+      <c r="C319" t="inlineStr">
+        <is>
+          <t>-35.63567786818645,174.530543271977</t>
+        </is>
+      </c>
+      <c r="D319" t="inlineStr">
+        <is>
+          <t>-35.635137433253675,174.53001505916166</t>
+        </is>
+      </c>
+      <c r="E319" t="inlineStr">
+        <is>
+          <t>-35.634780577426184,174.52925314140194</t>
+        </is>
+      </c>
+      <c r="F319" t="inlineStr">
+        <is>
+          <t>-35.63460507269671,174.52838127675264</t>
+        </is>
+      </c>
+      <c r="G319" t="inlineStr">
+        <is>
+          <t>-35.63463794308011,174.5274801491598</t>
+        </is>
+      </c>
+      <c r="H319" t="inlineStr">
+        <is>
+          <t>-35.63477317776288,174.52659355194726</t>
+        </is>
+      </c>
+      <c r="I319" t="inlineStr">
+        <is>
+          <t>-35.63487177528948,174.52570442160683</t>
+        </is>
+      </c>
+      <c r="J319" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="320">
+      <c r="A320" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-24 22:12:07+00:00</t>
+        </is>
+      </c>
+      <c r="B320" t="inlineStr">
+        <is>
+          <t>-35.63645161763604,174.53045577068406</t>
+        </is>
+      </c>
+      <c r="C320" t="inlineStr">
+        <is>
+          <t>-35.63566669628162,174.5305650587509</t>
+        </is>
+      </c>
+      <c r="D320" t="inlineStr">
+        <is>
+          <t>-35.6351377263672,174.53001480192754</t>
+        </is>
+      </c>
+      <c r="E320" t="inlineStr">
+        <is>
+          <t>-35.63478186517156,174.5292526362961</t>
+        </is>
+      </c>
+      <c r="F320" t="inlineStr">
+        <is>
+          <t>-35.63460750245117,174.5283811032676</t>
+        </is>
+      </c>
+      <c r="G320" t="inlineStr">
+        <is>
+          <t>-35.634638032941,174.52748015789945</t>
+        </is>
+      </c>
+      <c r="H320" t="inlineStr">
+        <is>
+          <t>-35.63477057882897,174.52659320675454</t>
+        </is>
+      </c>
+      <c r="I320" t="inlineStr">
+        <is>
+          <t>-35.63487696332542,174.52570521525234</t>
+        </is>
+      </c>
+      <c r="J320" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0093/nzd0093.xlsx
+++ b/data/nzd0093/nzd0093.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J320"/>
+  <dimension ref="A1:J322"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11934,7 +11934,7 @@
         </is>
       </c>
       <c r="B320" t="n">
-        <v>412.05</v>
+        <v>407.05</v>
       </c>
       <c r="C320" t="n">
         <v>373.11</v>
@@ -11960,6 +11960,78 @@
       <c r="J320" t="inlineStr">
         <is>
           <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="321">
+      <c r="A321" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-17 22:11:50+00:00</t>
+        </is>
+      </c>
+      <c r="B321" t="n">
+        <v>408.69</v>
+      </c>
+      <c r="C321" t="n">
+        <v>372.66</v>
+      </c>
+      <c r="D321" t="n">
+        <v>370.95</v>
+      </c>
+      <c r="E321" t="n">
+        <v>365.06</v>
+      </c>
+      <c r="F321" t="n">
+        <v>363.48</v>
+      </c>
+      <c r="G321" t="n">
+        <v>360.18</v>
+      </c>
+      <c r="H321" t="n">
+        <v>367.41</v>
+      </c>
+      <c r="I321" t="n">
+        <v>371.48</v>
+      </c>
+      <c r="J321" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="322">
+      <c r="A322" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-05 22:11:44+00:00</t>
+        </is>
+      </c>
+      <c r="B322" t="n">
+        <v>407.65</v>
+      </c>
+      <c r="C322" t="n">
+        <v>372.16</v>
+      </c>
+      <c r="D322" t="n">
+        <v>371</v>
+      </c>
+      <c r="E322" t="n">
+        <v>365.25</v>
+      </c>
+      <c r="F322" t="n">
+        <v>362.93</v>
+      </c>
+      <c r="G322" t="n">
+        <v>358.86</v>
+      </c>
+      <c r="H322" t="n">
+        <v>367.03</v>
+      </c>
+      <c r="I322" t="n">
+        <v>370.42</v>
+      </c>
+      <c r="J322" t="inlineStr">
+        <is>
+          <t>L8</t>
         </is>
       </c>
     </row>
@@ -11974,7 +12046,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B333"/>
+  <dimension ref="A1:B335"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15307,6 +15379,26 @@
       </c>
       <c r="B333" t="n">
         <v>0.67</v>
+      </c>
+    </row>
+    <row r="334">
+      <c r="A334" t="inlineStr">
+        <is>
+          <t>2026-02-17 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B334" t="n">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="335">
+      <c r="A335" t="inlineStr">
+        <is>
+          <t>2026-03-05 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B335" t="n">
+        <v>0.88</v>
       </c>
     </row>
   </sheetData>
@@ -15475,28 +15567,28 @@
         <v>0.0154</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.3068484816294428</v>
+        <v>-0.3210601271422966</v>
       </c>
       <c r="J2" t="n">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="K2" t="n">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="L2" t="n">
-        <v>0.02977854863765528</v>
+        <v>0.0328052944447188</v>
       </c>
       <c r="M2" t="n">
-        <v>9.836638070341939</v>
+        <v>9.856513071121528</v>
       </c>
       <c r="N2" t="n">
-        <v>163.148513287883</v>
+        <v>162.8382080964045</v>
       </c>
       <c r="O2" t="n">
-        <v>12.77296023981454</v>
+        <v>12.76080750173768</v>
       </c>
       <c r="P2" t="n">
-        <v>425.1151051098108</v>
+        <v>425.2664448293164</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -15553,28 +15645,28 @@
         <v>0.0622</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.1847000430121691</v>
+        <v>-0.1822664619137698</v>
       </c>
       <c r="J3" t="n">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="K3" t="n">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="L3" t="n">
-        <v>0.05980988400278353</v>
+        <v>0.05904818539552925</v>
       </c>
       <c r="M3" t="n">
-        <v>3.908179251005012</v>
+        <v>3.891896284203241</v>
       </c>
       <c r="N3" t="n">
-        <v>28.51967237211483</v>
+        <v>28.36533731225535</v>
       </c>
       <c r="O3" t="n">
-        <v>5.340381294637568</v>
+        <v>5.325911876125566</v>
       </c>
       <c r="P3" t="n">
-        <v>375.3506354507362</v>
+        <v>375.3247028188974</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -15631,28 +15723,28 @@
         <v>0.07290000000000001</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.108457599042809</v>
+        <v>-0.1050372275611957</v>
       </c>
       <c r="J4" t="n">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="K4" t="n">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="L4" t="n">
-        <v>0.04274553438250073</v>
+        <v>0.04060455817590902</v>
       </c>
       <c r="M4" t="n">
-        <v>2.850792114474525</v>
+        <v>2.846256274807139</v>
       </c>
       <c r="N4" t="n">
-        <v>14.00955821789609</v>
+        <v>13.96763762916334</v>
       </c>
       <c r="O4" t="n">
-        <v>3.742934439433329</v>
+        <v>3.737330280984454</v>
       </c>
       <c r="P4" t="n">
-        <v>371.1132127406606</v>
+        <v>371.0767599681029</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -15709,28 +15801,28 @@
         <v>0.0675</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.06865499229346975</v>
+        <v>-0.06336171163768352</v>
       </c>
       <c r="J5" t="n">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="K5" t="n">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="L5" t="n">
-        <v>0.01193572027860035</v>
+        <v>0.01026991580677095</v>
       </c>
       <c r="M5" t="n">
-        <v>3.475614021095428</v>
+        <v>3.475886849860867</v>
       </c>
       <c r="N5" t="n">
-        <v>20.75145868873314</v>
+        <v>20.73085848951259</v>
       </c>
       <c r="O5" t="n">
-        <v>4.5553768986477</v>
+        <v>4.553115251068502</v>
       </c>
       <c r="P5" t="n">
-        <v>362.748995847115</v>
+        <v>362.692581779498</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -15787,28 +15879,28 @@
         <v>0.0752</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.06154515935294589</v>
+        <v>-0.05166077717606586</v>
       </c>
       <c r="J6" t="n">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="K6" t="n">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="L6" t="n">
-        <v>0.007344244088099305</v>
+        <v>0.005184876292227192</v>
       </c>
       <c r="M6" t="n">
-        <v>4.115649824382222</v>
+        <v>4.141671294643014</v>
       </c>
       <c r="N6" t="n">
-        <v>27.22746332405548</v>
+        <v>27.43717848371187</v>
       </c>
       <c r="O6" t="n">
-        <v>5.217994185897056</v>
+        <v>5.23805101957893</v>
       </c>
       <c r="P6" t="n">
-        <v>356.953368163197</v>
+        <v>356.8480293253817</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -15865,28 +15957,28 @@
         <v>0.1169</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.06884687330814453</v>
+        <v>-0.063058651842547</v>
       </c>
       <c r="J7" t="n">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="K7" t="n">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="L7" t="n">
-        <v>0.01840918827317473</v>
+        <v>0.0155484274198715</v>
       </c>
       <c r="M7" t="n">
-        <v>2.700232582439363</v>
+        <v>2.708990710244894</v>
       </c>
       <c r="N7" t="n">
-        <v>13.4410162449997</v>
+        <v>13.48996575066495</v>
       </c>
       <c r="O7" t="n">
-        <v>3.666199155119604</v>
+        <v>3.67286887196711</v>
       </c>
       <c r="P7" t="n">
-        <v>356.7218190361372</v>
+        <v>356.6601397086167</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -15943,28 +16035,28 @@
         <v>0.07389999999999999</v>
       </c>
       <c r="I8" t="n">
-        <v>-5.696324037988919e-05</v>
+        <v>0.004255423127760628</v>
       </c>
       <c r="J8" t="n">
+        <v>321</v>
+      </c>
+      <c r="K8" t="n">
         <v>319</v>
       </c>
-      <c r="K8" t="n">
-        <v>317</v>
-      </c>
       <c r="L8" t="n">
-        <v>1.117551107210346e-08</v>
+        <v>6.293653974420721e-05</v>
       </c>
       <c r="M8" t="n">
-        <v>2.878033382490156</v>
+        <v>2.878520541478546</v>
       </c>
       <c r="N8" t="n">
-        <v>15.19867233633172</v>
+        <v>15.1741650420527</v>
       </c>
       <c r="O8" t="n">
-        <v>3.898547464932513</v>
+        <v>3.895403065416042</v>
       </c>
       <c r="P8" t="n">
-        <v>363.829113958398</v>
+        <v>363.7826209982571</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -16021,28 +16113,28 @@
         <v>0.09520000000000001</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.1439314345783659</v>
+        <v>-0.1366769699844231</v>
       </c>
       <c r="J9" t="n">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="K9" t="n">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="L9" t="n">
-        <v>0.05538316877496163</v>
+        <v>0.05034606721981627</v>
       </c>
       <c r="M9" t="n">
-        <v>3.2288674116542</v>
+        <v>3.23927290280287</v>
       </c>
       <c r="N9" t="n">
-        <v>18.7913077473735</v>
+        <v>18.88009181441685</v>
       </c>
       <c r="O9" t="n">
-        <v>4.334894202558293</v>
+        <v>4.345122761719955</v>
       </c>
       <c r="P9" t="n">
-        <v>368.97166783105</v>
+        <v>368.8943604101818</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -16080,7 +16172,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J320"/>
+  <dimension ref="A1:J322"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -32671,7 +32763,7 @@
       </c>
       <c r="B320" t="inlineStr">
         <is>
-          <t>-35.63645161763604,174.53045577068406</t>
+          <t>-35.636435801741754,174.5305074713166</t>
         </is>
       </c>
       <c r="C320" t="inlineStr">
@@ -32712,6 +32804,110 @@
       <c r="J320" t="inlineStr">
         <is>
           <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="321">
+      <c r="A321" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-17 22:11:50+00:00</t>
+        </is>
+      </c>
+      <c r="B321" t="inlineStr">
+        <is>
+          <t>-35.63644098935746,174.53049051351147</t>
+        </is>
+      </c>
+      <c r="C321" t="inlineStr">
+        <is>
+          <t>-35.63566453861716,174.53056926649623</t>
+        </is>
+      </c>
+      <c r="D321" t="inlineStr">
+        <is>
+          <t>-35.635152235486025,174.53000206883718</t>
+        </is>
+      </c>
+      <c r="E321" t="inlineStr">
+        <is>
+          <t>-35.63480040870484,174.52924536277035</t>
+        </is>
+      </c>
+      <c r="F321" t="inlineStr">
+        <is>
+          <t>-35.63464718844062,174.528378269678</t>
+        </is>
+      </c>
+      <c r="G321" t="inlineStr">
+        <is>
+          <t>-35.634657982055906,174.52748209810662</t>
+        </is>
+      </c>
+      <c r="H321" t="inlineStr">
+        <is>
+          <t>-35.63478213960392,174.52659474226706</t>
+        </is>
+      </c>
+      <c r="I321" t="inlineStr">
+        <is>
+          <t>-35.63490138287375,174.52570895086134</t>
+        </is>
+      </c>
+      <c r="J321" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="322">
+      <c r="A322" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-05 22:11:44+00:00</t>
+        </is>
+      </c>
+      <c r="B322" t="inlineStr">
+        <is>
+          <t>-35.6364376996502,174.53050126724182</t>
+        </is>
+      </c>
+      <c r="C322" t="inlineStr">
+        <is>
+          <t>-35.635662141212045,174.53057394176855</t>
+        </is>
+      </c>
+      <c r="D322" t="inlineStr">
+        <is>
+          <t>-35.6351526018779,174.53000174729442</t>
+        </is>
+      </c>
+      <c r="E322" t="inlineStr">
+        <is>
+          <t>-35.63480203984895,174.52924472296934</t>
+        </is>
+      </c>
+      <c r="F322" t="inlineStr">
+        <is>
+          <t>-35.634642238940806,174.52837862307365</t>
+        </is>
+      </c>
+      <c r="G322" t="inlineStr">
+        <is>
+          <t>-35.63464612042004,174.5274809444698</t>
+        </is>
+      </c>
+      <c r="H322" t="inlineStr">
+        <is>
+          <t>-35.63477873410433,174.5265942899455</t>
+        </is>
+      </c>
+      <c r="I322" t="inlineStr">
+        <is>
+          <t>-35.63489190129092,174.52570750040482</t>
+        </is>
+      </c>
+      <c r="J322" t="inlineStr">
+        <is>
+          <t>L8</t>
         </is>
       </c>
     </row>

--- a/data/nzd0093/nzd0093.xlsx
+++ b/data/nzd0093/nzd0093.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J322"/>
+  <dimension ref="A1:J324"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12032,6 +12032,78 @@
       <c r="J322" t="inlineStr">
         <is>
           <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="323">
+      <c r="A323" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-21 22:11:34+00:00</t>
+        </is>
+      </c>
+      <c r="B323" t="n">
+        <v>405.88</v>
+      </c>
+      <c r="C323" t="n">
+        <v>371.32</v>
+      </c>
+      <c r="D323" t="n">
+        <v>370.87</v>
+      </c>
+      <c r="E323" t="n">
+        <v>365.07</v>
+      </c>
+      <c r="F323" t="n">
+        <v>361.88</v>
+      </c>
+      <c r="G323" t="n">
+        <v>358.19</v>
+      </c>
+      <c r="H323" t="n">
+        <v>366.92</v>
+      </c>
+      <c r="I323" t="n">
+        <v>370.39</v>
+      </c>
+      <c r="J323" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="324">
+      <c r="A324" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-14 22:11:35+00:00</t>
+        </is>
+      </c>
+      <c r="B324" t="n">
+        <v>408.19</v>
+      </c>
+      <c r="C324" t="n">
+        <v>371.53</v>
+      </c>
+      <c r="D324" t="n">
+        <v>370.5</v>
+      </c>
+      <c r="E324" t="n">
+        <v>364.24</v>
+      </c>
+      <c r="F324" t="n">
+        <v>361.23</v>
+      </c>
+      <c r="G324" t="n">
+        <v>357.74</v>
+      </c>
+      <c r="H324" t="n">
+        <v>366.82</v>
+      </c>
+      <c r="I324" t="n">
+        <v>368.96</v>
+      </c>
+      <c r="J324" t="inlineStr">
+        <is>
+          <t>L9</t>
         </is>
       </c>
     </row>
@@ -12046,7 +12118,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B335"/>
+  <dimension ref="A1:B337"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15399,6 +15471,26 @@
       </c>
       <c r="B335" t="n">
         <v>0.88</v>
+      </c>
+    </row>
+    <row r="336">
+      <c r="A336" t="inlineStr">
+        <is>
+          <t>2026-03-21 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B336" t="n">
+        <v>0.97</v>
+      </c>
+    </row>
+    <row r="337">
+      <c r="A337" t="inlineStr">
+        <is>
+          <t>2026-04-14 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B337" t="n">
+        <v>-0.63</v>
       </c>
     </row>
   </sheetData>
@@ -15567,28 +15659,28 @@
         <v>0.0154</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.3210601271422966</v>
+        <v>-0.3331247205101939</v>
       </c>
       <c r="J2" t="n">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="K2" t="n">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="L2" t="n">
-        <v>0.0328052944447188</v>
+        <v>0.03557092376787152</v>
       </c>
       <c r="M2" t="n">
-        <v>9.856513071121528</v>
+        <v>9.864158123465526</v>
       </c>
       <c r="N2" t="n">
-        <v>162.8382080964045</v>
+        <v>162.4119398768365</v>
       </c>
       <c r="O2" t="n">
-        <v>12.76080750173768</v>
+        <v>12.74409431371396</v>
       </c>
       <c r="P2" t="n">
-        <v>425.2664448293164</v>
+        <v>425.3955426744516</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -15645,28 +15737,28 @@
         <v>0.0622</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.1822664619137698</v>
+        <v>-0.1811058205219632</v>
       </c>
       <c r="J3" t="n">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="K3" t="n">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="L3" t="n">
-        <v>0.05904818539552925</v>
+        <v>0.05908420196746611</v>
       </c>
       <c r="M3" t="n">
-        <v>3.891896284203241</v>
+        <v>3.87157417408807</v>
       </c>
       <c r="N3" t="n">
-        <v>28.36533731225535</v>
+        <v>28.19507674916507</v>
       </c>
       <c r="O3" t="n">
-        <v>5.325911876125566</v>
+        <v>5.3099036478231</v>
       </c>
       <c r="P3" t="n">
-        <v>375.3247028188974</v>
+        <v>375.3122791262845</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -15723,28 +15815,28 @@
         <v>0.07290000000000001</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.1050372275611957</v>
+        <v>-0.1020679684629095</v>
       </c>
       <c r="J4" t="n">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="K4" t="n">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="L4" t="n">
-        <v>0.04060455817590902</v>
+        <v>0.03884064184800495</v>
       </c>
       <c r="M4" t="n">
-        <v>2.846256274807139</v>
+        <v>2.840133742159749</v>
       </c>
       <c r="N4" t="n">
-        <v>13.96763762916334</v>
+        <v>13.91608332172531</v>
       </c>
       <c r="O4" t="n">
-        <v>3.737330280984454</v>
+        <v>3.73042669432403</v>
       </c>
       <c r="P4" t="n">
-        <v>371.0767599681029</v>
+        <v>371.0449852201493</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -15801,28 +15893,28 @@
         <v>0.0675</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.06336171163768352</v>
+        <v>-0.05884299740188371</v>
       </c>
       <c r="J5" t="n">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="K5" t="n">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="L5" t="n">
-        <v>0.01026991580677095</v>
+        <v>0.008955232491712262</v>
       </c>
       <c r="M5" t="n">
-        <v>3.475886849860867</v>
+        <v>3.472777523983652</v>
       </c>
       <c r="N5" t="n">
-        <v>20.73085848951259</v>
+        <v>20.68402528986815</v>
       </c>
       <c r="O5" t="n">
-        <v>4.553115251068502</v>
+        <v>4.547969358941213</v>
       </c>
       <c r="P5" t="n">
-        <v>362.692581779498</v>
+        <v>362.6442286272264</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -15879,28 +15971,28 @@
         <v>0.0752</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.05166077717606586</v>
+        <v>-0.04411786486821465</v>
       </c>
       <c r="J6" t="n">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="K6" t="n">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="L6" t="n">
-        <v>0.005184876292227192</v>
+        <v>0.003807102105195526</v>
       </c>
       <c r="M6" t="n">
-        <v>4.141671294643014</v>
+        <v>4.155889984950117</v>
       </c>
       <c r="N6" t="n">
-        <v>27.43717848371187</v>
+        <v>27.49203999819828</v>
       </c>
       <c r="O6" t="n">
-        <v>5.23805101957893</v>
+        <v>5.243285229529124</v>
       </c>
       <c r="P6" t="n">
-        <v>356.8480293253817</v>
+        <v>356.7673082886739</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -15957,28 +16049,28 @@
         <v>0.1169</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.063058651842547</v>
+        <v>-0.05936216427988033</v>
       </c>
       <c r="J7" t="n">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="K7" t="n">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="L7" t="n">
-        <v>0.0155484274198715</v>
+        <v>0.01393447761262889</v>
       </c>
       <c r="M7" t="n">
-        <v>2.708990710244894</v>
+        <v>2.708658391590792</v>
       </c>
       <c r="N7" t="n">
-        <v>13.48996575066495</v>
+        <v>13.46057502607225</v>
       </c>
       <c r="O7" t="n">
-        <v>3.67286887196711</v>
+        <v>3.668865632054716</v>
       </c>
       <c r="P7" t="n">
-        <v>356.6601397086167</v>
+        <v>356.6205827098697</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -16035,28 +16127,28 @@
         <v>0.07389999999999999</v>
       </c>
       <c r="I8" t="n">
-        <v>0.004255423127760628</v>
+        <v>0.008001350436041046</v>
       </c>
       <c r="J8" t="n">
+        <v>323</v>
+      </c>
+      <c r="K8" t="n">
         <v>321</v>
       </c>
-      <c r="K8" t="n">
-        <v>319</v>
-      </c>
       <c r="L8" t="n">
-        <v>6.293653974420721e-05</v>
+        <v>0.0002247339732995846</v>
       </c>
       <c r="M8" t="n">
-        <v>2.878520541478546</v>
+        <v>2.8768575011838</v>
       </c>
       <c r="N8" t="n">
-        <v>15.1741650420527</v>
+        <v>15.13369907087711</v>
       </c>
       <c r="O8" t="n">
-        <v>3.895403065416042</v>
+        <v>3.890205530672783</v>
       </c>
       <c r="P8" t="n">
-        <v>363.7826209982571</v>
+        <v>363.7420657816906</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -16113,28 +16205,28 @@
         <v>0.09520000000000001</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.1366769699844231</v>
+        <v>-0.1312131920059327</v>
       </c>
       <c r="J9" t="n">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="K9" t="n">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="L9" t="n">
-        <v>0.05034606721981627</v>
+        <v>0.04690580794399024</v>
       </c>
       <c r="M9" t="n">
-        <v>3.23927290280287</v>
+        <v>3.242936456224407</v>
       </c>
       <c r="N9" t="n">
-        <v>18.88009181441685</v>
+        <v>18.88396911969906</v>
       </c>
       <c r="O9" t="n">
-        <v>4.345122761719955</v>
+        <v>4.345568906334251</v>
       </c>
       <c r="P9" t="n">
-        <v>368.8943604101818</v>
+        <v>368.8358983428402</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -16172,7 +16264,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J322"/>
+  <dimension ref="A1:J324"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -32911,6 +33003,110 @@
         </is>
       </c>
     </row>
+    <row r="323">
+      <c r="A323" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-21 22:11:34+00:00</t>
+        </is>
+      </c>
+      <c r="B323" t="inlineStr">
+        <is>
+          <t>-35.63643210081934,174.53051956926157</t>
+        </is>
+      </c>
+      <c r="C323" t="inlineStr">
+        <is>
+          <t>-35.63565811357105,174.53058179622542</t>
+        </is>
+      </c>
+      <c r="D323" t="inlineStr">
+        <is>
+          <t>-35.63515164925903,174.53000258330556</t>
+        </is>
+      </c>
+      <c r="E323" t="inlineStr">
+        <is>
+          <t>-35.634800494554526,174.52924532909663</t>
+        </is>
+      </c>
+      <c r="F323" t="inlineStr">
+        <is>
+          <t>-35.63463278989572,174.52837929773796</t>
+        </is>
+      </c>
+      <c r="G323" t="inlineStr">
+        <is>
+          <t>-35.6346400997412,174.52748035891184</t>
+        </is>
+      </c>
+      <c r="H323" t="inlineStr">
+        <is>
+          <t>-35.63477774830181,174.5265941590103</t>
+        </is>
+      </c>
+      <c r="I323" t="inlineStr">
+        <is>
+          <t>-35.63489163294423,174.52570745935415</t>
+        </is>
+      </c>
+      <c r="J323" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="324">
+      <c r="A324" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-14 22:11:35+00:00</t>
+        </is>
+      </c>
+      <c r="B324" t="inlineStr">
+        <is>
+          <t>-35.63643940776757,174.53049568357423</t>
+        </is>
+      </c>
+      <c r="C324" t="inlineStr">
+        <is>
+          <t>-35.635659120481336,174.53057983261127</t>
+        </is>
+      </c>
+      <c r="D324" t="inlineStr">
+        <is>
+          <t>-35.63514893795913,174.53000496272173</t>
+        </is>
+      </c>
+      <c r="E324" t="inlineStr">
+        <is>
+          <t>-35.63479336903022,174.52924812401665</t>
+        </is>
+      </c>
+      <c r="F324" t="inlineStr">
+        <is>
+          <t>-35.63462694048684,174.52837971538725</t>
+        </is>
+      </c>
+      <c r="G324" t="inlineStr">
+        <is>
+          <t>-35.63463605600168,174.52747996562672</t>
+        </is>
+      </c>
+      <c r="H324" t="inlineStr">
+        <is>
+          <t>-35.63477685211771,174.52659403997833</t>
+        </is>
+      </c>
+      <c r="I324" t="inlineStr">
+        <is>
+          <t>-35.634878841752226,174.52570550260683</t>
+        </is>
+      </c>
+      <c r="J324" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0093/nzd0093.xlsx
+++ b/data/nzd0093/nzd0093.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J324"/>
+  <dimension ref="A1:J326"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12102,6 +12102,78 @@
         <v>368.96</v>
       </c>
       <c r="J324" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="325">
+      <c r="A325" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-08 22:11:04+00:00</t>
+        </is>
+      </c>
+      <c r="B325" t="n">
+        <v>408.19</v>
+      </c>
+      <c r="C325" t="n">
+        <v>369.34</v>
+      </c>
+      <c r="D325" t="n">
+        <v>369.88</v>
+      </c>
+      <c r="E325" t="n">
+        <v>364.43</v>
+      </c>
+      <c r="F325" t="n">
+        <v>359.9</v>
+      </c>
+      <c r="G325" t="n">
+        <v>357.12</v>
+      </c>
+      <c r="H325" t="n">
+        <v>365.54</v>
+      </c>
+      <c r="I325" t="n">
+        <v>368.05</v>
+      </c>
+      <c r="J325" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="326">
+      <c r="A326" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-16 22:11:13+00:00</t>
+        </is>
+      </c>
+      <c r="B326" t="n">
+        <v>410.03</v>
+      </c>
+      <c r="C326" t="n">
+        <v>368.9</v>
+      </c>
+      <c r="D326" t="n">
+        <v>369.7</v>
+      </c>
+      <c r="E326" t="n">
+        <v>363.5</v>
+      </c>
+      <c r="F326" t="n">
+        <v>359.9</v>
+      </c>
+      <c r="G326" t="n">
+        <v>357.12</v>
+      </c>
+      <c r="H326" t="n">
+        <v>365.54</v>
+      </c>
+      <c r="I326" t="n">
+        <v>368.05</v>
+      </c>
+      <c r="J326" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -12118,7 +12190,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B337"/>
+  <dimension ref="A1:B339"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15491,6 +15563,26 @@
       </c>
       <c r="B337" t="n">
         <v>-0.63</v>
+      </c>
+    </row>
+    <row r="338">
+      <c r="A338" t="inlineStr">
+        <is>
+          <t>2026-05-08 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B338" t="n">
+        <v>0.17</v>
+      </c>
+    </row>
+    <row r="339">
+      <c r="A339" t="inlineStr">
+        <is>
+          <t>2026-05-16 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B339" t="n">
+        <v>-0.12</v>
       </c>
     </row>
   </sheetData>
@@ -15659,28 +15751,28 @@
         <v>0.0154</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.3331247205101939</v>
+        <v>-0.3422412077580673</v>
       </c>
       <c r="J2" t="n">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="K2" t="n">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="L2" t="n">
-        <v>0.03557092376787152</v>
+        <v>0.03788569179696821</v>
       </c>
       <c r="M2" t="n">
-        <v>9.864158123465526</v>
+        <v>9.854775812460321</v>
       </c>
       <c r="N2" t="n">
-        <v>162.4119398768365</v>
+        <v>161.7494702287554</v>
       </c>
       <c r="O2" t="n">
-        <v>12.74409431371396</v>
+        <v>12.7180765145031</v>
       </c>
       <c r="P2" t="n">
-        <v>425.3955426744516</v>
+        <v>425.4935603708137</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -15737,28 +15829,28 @@
         <v>0.0622</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.1811058205219632</v>
+        <v>-0.1827918556834243</v>
       </c>
       <c r="J3" t="n">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="K3" t="n">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="L3" t="n">
-        <v>0.05908420196746611</v>
+        <v>0.06086873099751711</v>
       </c>
       <c r="M3" t="n">
-        <v>3.87157417408807</v>
+        <v>3.858909866884976</v>
       </c>
       <c r="N3" t="n">
-        <v>28.19507674916507</v>
+        <v>28.03319207375205</v>
       </c>
       <c r="O3" t="n">
-        <v>5.3099036478231</v>
+        <v>5.29463804936202</v>
       </c>
       <c r="P3" t="n">
-        <v>375.3122791262845</v>
+        <v>375.3304092577518</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -15815,28 +15907,28 @@
         <v>0.07290000000000001</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.1020679684629095</v>
+        <v>-0.1002652594424963</v>
       </c>
       <c r="J4" t="n">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="K4" t="n">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="L4" t="n">
-        <v>0.03884064184800495</v>
+        <v>0.03798943547737033</v>
       </c>
       <c r="M4" t="n">
-        <v>2.840133742159749</v>
+        <v>2.82951577792652</v>
       </c>
       <c r="N4" t="n">
-        <v>13.91608332172531</v>
+        <v>13.84346417009692</v>
       </c>
       <c r="O4" t="n">
-        <v>3.73042669432403</v>
+        <v>3.720680605762461</v>
       </c>
       <c r="P4" t="n">
-        <v>371.0449852201493</v>
+        <v>371.0256024616341</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -15893,28 +15985,28 @@
         <v>0.0675</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.05884299740188371</v>
+        <v>-0.05529434087977717</v>
       </c>
       <c r="J5" t="n">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="K5" t="n">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="L5" t="n">
-        <v>0.008955232491712262</v>
+        <v>0.008003053227840451</v>
       </c>
       <c r="M5" t="n">
-        <v>3.472777523983652</v>
+        <v>3.46561148588502</v>
       </c>
       <c r="N5" t="n">
-        <v>20.68402528986815</v>
+        <v>20.60833080237837</v>
       </c>
       <c r="O5" t="n">
-        <v>4.547969358941213</v>
+        <v>4.539639941931339</v>
       </c>
       <c r="P5" t="n">
-        <v>362.6442286272264</v>
+        <v>362.6060751966969</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -15971,28 +16063,28 @@
         <v>0.0752</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.04411786486821465</v>
+        <v>-0.03882403780648236</v>
       </c>
       <c r="J6" t="n">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="K6" t="n">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="L6" t="n">
-        <v>0.003807102105195526</v>
+        <v>0.002978740691456871</v>
       </c>
       <c r="M6" t="n">
-        <v>4.155889984950117</v>
+        <v>4.158358597811392</v>
       </c>
       <c r="N6" t="n">
-        <v>27.49203999819828</v>
+        <v>27.43468252179873</v>
       </c>
       <c r="O6" t="n">
-        <v>5.243285229529124</v>
+        <v>5.237812761239059</v>
       </c>
       <c r="P6" t="n">
-        <v>356.7673082886739</v>
+        <v>356.710387333721</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -16049,28 +16141,28 @@
         <v>0.1169</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.05936216427988033</v>
+        <v>-0.05680874597520676</v>
       </c>
       <c r="J7" t="n">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="K7" t="n">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="L7" t="n">
-        <v>0.01393447761262889</v>
+        <v>0.01292353964068449</v>
       </c>
       <c r="M7" t="n">
-        <v>2.708658391590792</v>
+        <v>2.703295545711742</v>
       </c>
       <c r="N7" t="n">
-        <v>13.46057502607225</v>
+        <v>13.40375671769069</v>
       </c>
       <c r="O7" t="n">
-        <v>3.668865632054716</v>
+        <v>3.661114136119043</v>
       </c>
       <c r="P7" t="n">
-        <v>356.6205827098697</v>
+        <v>356.5931275209687</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -16127,28 +16219,28 @@
         <v>0.07389999999999999</v>
       </c>
       <c r="I8" t="n">
-        <v>0.008001350436041046</v>
+        <v>0.009975006004503474</v>
       </c>
       <c r="J8" t="n">
+        <v>325</v>
+      </c>
+      <c r="K8" t="n">
         <v>323</v>
       </c>
-      <c r="K8" t="n">
-        <v>321</v>
-      </c>
       <c r="L8" t="n">
-        <v>0.0002247339732995846</v>
+        <v>0.0003536622383202292</v>
       </c>
       <c r="M8" t="n">
-        <v>2.8768575011838</v>
+        <v>2.867581950079434</v>
       </c>
       <c r="N8" t="n">
-        <v>15.13369907087711</v>
+        <v>15.0551977238286</v>
       </c>
       <c r="O8" t="n">
-        <v>3.890205530672783</v>
+        <v>3.880102798100664</v>
       </c>
       <c r="P8" t="n">
-        <v>363.7420657816906</v>
+        <v>363.7205989009507</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -16205,28 +16297,28 @@
         <v>0.09520000000000001</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.1312131920059327</v>
+        <v>-0.1278866976419006</v>
       </c>
       <c r="J9" t="n">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="K9" t="n">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="L9" t="n">
-        <v>0.04690580794399024</v>
+        <v>0.04514225505560887</v>
       </c>
       <c r="M9" t="n">
-        <v>3.242936456224407</v>
+        <v>3.237373655802494</v>
       </c>
       <c r="N9" t="n">
-        <v>18.88396911969906</v>
+        <v>18.81191407885886</v>
       </c>
       <c r="O9" t="n">
-        <v>4.345568906334251</v>
+        <v>4.337270348832185</v>
       </c>
       <c r="P9" t="n">
-        <v>368.8358983428402</v>
+        <v>368.8001307835962</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -16264,7 +16356,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J324"/>
+  <dimension ref="A1:J326"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -33107,6 +33199,110 @@
         </is>
       </c>
     </row>
+    <row r="325">
+      <c r="A325" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-08 22:11:04+00:00</t>
+        </is>
+      </c>
+      <c r="B325" t="inlineStr">
+        <is>
+          <t>-35.63643940776757,174.53049568357423</t>
+        </is>
+      </c>
+      <c r="C325" t="inlineStr">
+        <is>
+          <t>-35.63564861984386,174.53060031029912</t>
+        </is>
+      </c>
+      <c r="D325" t="inlineStr">
+        <is>
+          <t>-35.635144394699736,174.5300089498512</t>
+        </is>
+      </c>
+      <c r="E325" t="inlineStr">
+        <is>
+          <t>-35.63479500017434,174.5292474842157</t>
+        </is>
+      </c>
+      <c r="F325" t="inlineStr">
+        <is>
+          <t>-35.63461497169636,174.5283805699618</t>
+        </is>
+      </c>
+      <c r="G325" t="inlineStr">
+        <is>
+          <t>-35.63463048462721,174.5274794237673</t>
+        </is>
+      </c>
+      <c r="H325" t="inlineStr">
+        <is>
+          <t>-35.63476538096114,174.52659251636922</t>
+        </is>
+      </c>
+      <c r="I325" t="inlineStr">
+        <is>
+          <t>-35.634870701902734,174.52570425740433</t>
+        </is>
+      </c>
+      <c r="J325" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="326">
+      <c r="A326" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-16 22:11:13+00:00</t>
+        </is>
+      </c>
+      <c r="B326" t="inlineStr">
+        <is>
+          <t>-35.63644522801736,174.53047665774216</t>
+        </is>
+      </c>
+      <c r="C326" t="inlineStr">
+        <is>
+          <t>-35.63564651012634,174.5306044245371</t>
+        </is>
+      </c>
+      <c r="D326" t="inlineStr">
+        <is>
+          <t>-35.63514307568893,174.53001010740485</t>
+        </is>
+      </c>
+      <c r="E326" t="inlineStr">
+        <is>
+          <t>-35.634787016153076,174.5292506158726</t>
+        </is>
+      </c>
+      <c r="F326" t="inlineStr">
+        <is>
+          <t>-35.63461497169636,174.5283805699618</t>
+        </is>
+      </c>
+      <c r="G326" t="inlineStr">
+        <is>
+          <t>-35.63463048462721,174.5274794237673</t>
+        </is>
+      </c>
+      <c r="H326" t="inlineStr">
+        <is>
+          <t>-35.63476538096114,174.52659251636922</t>
+        </is>
+      </c>
+      <c r="I326" t="inlineStr">
+        <is>
+          <t>-35.634870701902734,174.52570425740433</t>
+        </is>
+      </c>
+      <c r="J326" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0093/nzd0093.xlsx
+++ b/data/nzd0093/nzd0093.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J326"/>
+  <dimension ref="A1:J327"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12176,6 +12176,42 @@
       <c r="J326" t="inlineStr">
         <is>
           <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="327">
+      <c r="A327" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-09 22:10:54+00:00</t>
+        </is>
+      </c>
+      <c r="B327" t="n">
+        <v>413.75</v>
+      </c>
+      <c r="C327" t="n">
+        <v>367.91</v>
+      </c>
+      <c r="D327" t="n">
+        <v>369.65</v>
+      </c>
+      <c r="E327" t="n">
+        <v>363.37</v>
+      </c>
+      <c r="F327" t="n">
+        <v>358.46</v>
+      </c>
+      <c r="G327" t="n">
+        <v>356.11</v>
+      </c>
+      <c r="H327" t="n">
+        <v>364.65</v>
+      </c>
+      <c r="I327" t="n">
+        <v>367.55</v>
+      </c>
+      <c r="J327" t="inlineStr">
+        <is>
+          <t>L8</t>
         </is>
       </c>
     </row>
@@ -12190,7 +12226,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B339"/>
+  <dimension ref="A1:B340"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15583,6 +15619,16 @@
       </c>
       <c r="B339" t="n">
         <v>-0.12</v>
+      </c>
+    </row>
+    <row r="340">
+      <c r="A340" t="inlineStr">
+        <is>
+          <t>2026-06-09 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B340" t="n">
+        <v>-0.46</v>
       </c>
     </row>
   </sheetData>
@@ -15751,28 +15797,28 @@
         <v>0.0154</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.3422412077580673</v>
+        <v>-0.343836257292551</v>
       </c>
       <c r="J2" t="n">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="K2" t="n">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="L2" t="n">
-        <v>0.03788569179696821</v>
+        <v>0.03846968424108055</v>
       </c>
       <c r="M2" t="n">
-        <v>9.854775812460321</v>
+        <v>9.833441348805717</v>
       </c>
       <c r="N2" t="n">
-        <v>161.7494702287554</v>
+        <v>161.27386284173</v>
       </c>
       <c r="O2" t="n">
-        <v>12.7180765145031</v>
+        <v>12.69936466291641</v>
       </c>
       <c r="P2" t="n">
-        <v>425.4935603708137</v>
+        <v>425.510766782376</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -15829,28 +15875,28 @@
         <v>0.0622</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.1827918556834243</v>
+        <v>-0.1843467534505955</v>
       </c>
       <c r="J3" t="n">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="K3" t="n">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="L3" t="n">
-        <v>0.06086873099751711</v>
+        <v>0.06219534544212002</v>
       </c>
       <c r="M3" t="n">
-        <v>3.858909866884976</v>
+        <v>3.857273042102823</v>
       </c>
       <c r="N3" t="n">
-        <v>28.03319207375205</v>
+        <v>27.96673541164833</v>
       </c>
       <c r="O3" t="n">
-        <v>5.29463804936202</v>
+        <v>5.288358479873347</v>
       </c>
       <c r="P3" t="n">
-        <v>375.3304092577518</v>
+        <v>375.3471825367886</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -15907,28 +15953,28 @@
         <v>0.07290000000000001</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.1002652594424963</v>
+        <v>-0.09946668491737276</v>
       </c>
       <c r="J4" t="n">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="K4" t="n">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="L4" t="n">
-        <v>0.03798943547737033</v>
+        <v>0.03763890443570794</v>
       </c>
       <c r="M4" t="n">
-        <v>2.82951577792652</v>
+        <v>2.823841142119794</v>
       </c>
       <c r="N4" t="n">
-        <v>13.84346417009692</v>
+        <v>13.80615225204093</v>
       </c>
       <c r="O4" t="n">
-        <v>3.720680605762461</v>
+        <v>3.715663097219786</v>
       </c>
       <c r="P4" t="n">
-        <v>371.0256024616341</v>
+        <v>371.0169879317117</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -15985,28 +16031,28 @@
         <v>0.0675</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.05529434087977717</v>
+        <v>-0.05392258656390867</v>
       </c>
       <c r="J5" t="n">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="K5" t="n">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="L5" t="n">
-        <v>0.008003053227840451</v>
+        <v>0.007659292899055092</v>
       </c>
       <c r="M5" t="n">
-        <v>3.46561148588502</v>
+        <v>3.460522155207078</v>
       </c>
       <c r="N5" t="n">
-        <v>20.60833080237837</v>
+        <v>20.56031900852198</v>
       </c>
       <c r="O5" t="n">
-        <v>4.539639941931339</v>
+        <v>4.534348796522162</v>
       </c>
       <c r="P5" t="n">
-        <v>362.6060751966969</v>
+        <v>362.591277556366</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -16063,28 +16109,28 @@
         <v>0.0752</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.03882403780648236</v>
+        <v>-0.03711706917902893</v>
       </c>
       <c r="J6" t="n">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="K6" t="n">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="L6" t="n">
-        <v>0.002978740691456871</v>
+        <v>0.002739258349754192</v>
       </c>
       <c r="M6" t="n">
-        <v>4.158358597811392</v>
+        <v>4.154602170277404</v>
       </c>
       <c r="N6" t="n">
-        <v>27.43468252179873</v>
+        <v>27.37406966848757</v>
       </c>
       <c r="O6" t="n">
-        <v>5.237812761239059</v>
+        <v>5.232023477440403</v>
       </c>
       <c r="P6" t="n">
-        <v>356.710387333721</v>
+        <v>356.6919736079444</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -16141,28 +16187,28 @@
         <v>0.1169</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.05680874597520676</v>
+        <v>-0.05617702337620114</v>
       </c>
       <c r="J7" t="n">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="K7" t="n">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="L7" t="n">
-        <v>0.01292353964068449</v>
+        <v>0.01272259927443853</v>
       </c>
       <c r="M7" t="n">
-        <v>2.703295545711742</v>
+        <v>2.697770951345604</v>
       </c>
       <c r="N7" t="n">
-        <v>13.40375671769069</v>
+        <v>13.36586535543086</v>
       </c>
       <c r="O7" t="n">
-        <v>3.661114136119043</v>
+        <v>3.65593563338181</v>
       </c>
       <c r="P7" t="n">
-        <v>356.5931275209687</v>
+        <v>356.5863128868166</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -16219,28 +16265,28 @@
         <v>0.07389999999999999</v>
       </c>
       <c r="I8" t="n">
-        <v>0.009975006004503474</v>
+        <v>0.01038936507601538</v>
       </c>
       <c r="J8" t="n">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="K8" t="n">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="L8" t="n">
-        <v>0.0003536622383202292</v>
+        <v>0.0003862147001247873</v>
       </c>
       <c r="M8" t="n">
-        <v>2.867581950079434</v>
+        <v>2.860510087557752</v>
       </c>
       <c r="N8" t="n">
-        <v>15.0551977238286</v>
+        <v>15.01008828083722</v>
       </c>
       <c r="O8" t="n">
-        <v>3.880102798100664</v>
+        <v>3.874285518755326</v>
       </c>
       <c r="P8" t="n">
-        <v>363.7205989009507</v>
+        <v>363.7160775102462</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -16297,28 +16343,28 @@
         <v>0.09520000000000001</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.1278866976419006</v>
+        <v>-0.1265596256405685</v>
       </c>
       <c r="J9" t="n">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="K9" t="n">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="L9" t="n">
-        <v>0.04514225505560887</v>
+        <v>0.04450481626861635</v>
       </c>
       <c r="M9" t="n">
-        <v>3.237373655802494</v>
+        <v>3.23319350376534</v>
       </c>
       <c r="N9" t="n">
-        <v>18.81191407885886</v>
+        <v>18.76843841749481</v>
       </c>
       <c r="O9" t="n">
-        <v>4.337270348832185</v>
+        <v>4.332255580814088</v>
       </c>
       <c r="P9" t="n">
-        <v>368.8001307835962</v>
+        <v>368.7858151485428</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -16356,7 +16402,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J326"/>
+  <dimension ref="A1:J327"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -33303,6 +33349,58 @@
         </is>
       </c>
     </row>
+    <row r="327">
+      <c r="A327" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-09 22:10:54+00:00</t>
+        </is>
+      </c>
+      <c r="B327" t="inlineStr">
+        <is>
+          <t>-35.63645699503515,174.53043819246417</t>
+        </is>
+      </c>
+      <c r="C327" t="inlineStr">
+        <is>
+          <t>-35.635641763261425,174.53061368157182</t>
+        </is>
+      </c>
+      <c r="D327" t="inlineStr">
+        <is>
+          <t>-35.635142709297035,174.53001042894752</t>
+        </is>
+      </c>
+      <c r="E327" t="inlineStr">
+        <is>
+          <t>-35.63478590010708,174.52925105363104</t>
+        </is>
+      </c>
+      <c r="F327" t="inlineStr">
+        <is>
+          <t>-35.634602013005896,174.52838149521523</t>
+        </is>
+      </c>
+      <c r="G327" t="inlineStr">
+        <is>
+          <t>-35.63462140867846,174.52747854106101</t>
+        </is>
+      </c>
+      <c r="H327" t="inlineStr">
+        <is>
+          <t>-35.63475740492258,174.52659145698507</t>
+        </is>
+      </c>
+      <c r="I327" t="inlineStr">
+        <is>
+          <t>-35.63486622945795,174.52570357322725</t>
+        </is>
+      </c>
+      <c r="J327" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
